--- a/output/pdf_financials_xlsx/WPR.xlsx
+++ b/output/pdf_financials_xlsx/WPR.xlsx
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>3.377327</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>6.795018</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.132599</v>
+        <v>5.902213</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.074155</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002586</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.045569</v>
       </c>
     </row>
     <row r="13">
@@ -1116,10 +1116,10 @@
         <v>-3.554759</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.065119</v>
+        <v>-1.067705</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.583883</v>
+        <v>-1.629452</v>
       </c>
     </row>
     <row r="28">
@@ -1166,10 +1166,10 @@
         <v>-3.554759</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.065119</v>
+        <v>-1.067705</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.583883</v>
+        <v>-1.629452</v>
       </c>
     </row>
     <row r="30">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-27.16749426868175</v>
+        <v>-27.23345416628832</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-23.1145273715046</v>
+        <v>-23.77954233649387</v>
       </c>
     </row>
     <row r="31">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.240347</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.689481</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.072727</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.082611</v>
       </c>
     </row>
     <row r="125">
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.240347</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.689481</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.072727</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.082611</v>
       </c>
     </row>
     <row r="126">
@@ -8274,7 +8274,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -9734,7 +9738,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-0.240347</v>
       </c>
@@ -11104,7 +11112,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13480,7 +13488,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">

--- a/output/pdf_financials_xlsx/WPR.xlsx
+++ b/output/pdf_financials_xlsx/WPR.xlsx
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.014557</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.058228</v>
       </c>
     </row>
     <row r="29">
@@ -1166,10 +1166,10 @@
         <v>-3.554759</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.067705</v>
+        <v>-1.053148</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.629452</v>
+        <v>-1.571224</v>
       </c>
     </row>
     <row r="30">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-27.23345416628832</v>
+        <v>-26.86215554700803</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-23.77954233649387</v>
+        <v>-22.92978720951291</v>
       </c>
     </row>
     <row r="31">
@@ -2933,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.014557</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.058228</v>
       </c>
     </row>
     <row r="101">
@@ -7684,7 +7684,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WPR.xlsx
+++ b/output/pdf_financials_xlsx/WPR.xlsx
@@ -814,7 +814,7 @@
         <v>-1.065119</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1.583883</v>
+        <v>-1.332892</v>
       </c>
     </row>
     <row r="17">
@@ -839,7 +839,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.250991</v>
       </c>
     </row>
     <row r="18">
@@ -1119,7 +1119,7 @@
         <v>-1.067705</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.629452</v>
+        <v>-1.378461</v>
       </c>
     </row>
     <row r="28">
@@ -1169,7 +1169,7 @@
         <v>-1.053148</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.571224</v>
+        <v>-1.320233</v>
       </c>
     </row>
     <row r="30">
@@ -1196,7 +1196,7 @@
         <v>-26.86215554700803</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-22.92978720951291</v>
+        <v>-19.2669293219661</v>
       </c>
     </row>
     <row r="31">
@@ -1221,7 +1221,7 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-18.83055791466975</v>
       </c>
     </row>
     <row r="32">
@@ -1352,10 +1352,10 @@
         <v>0.021147</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>1.52027</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>5.158404</v>
       </c>
     </row>
     <row r="38">
@@ -1452,10 +1452,10 @@
         <v>0.021147</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>1.52027</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>5.158404</v>
       </c>
     </row>
     <row r="42">
@@ -1627,10 +1627,10 @@
         <v>1.86969</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.00679</v>
+        <v>2.48652</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6.587455</v>
+        <v>1.429051</v>
       </c>
     </row>
     <row r="49">
@@ -2039,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.745424</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.178121</v>
       </c>
     </row>
     <row r="65">
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.5328040000000001</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.902201</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.5944739999999999</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.885923</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.072225</v>
       </c>
     </row>
     <row r="68">
@@ -2139,10 +2139,10 @@
         <v>0.951758</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.810424</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>1.250346</v>
       </c>
     </row>
     <row r="69">
@@ -2314,10 +2314,10 @@
         <v>8.91499</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.164549</v>
+        <v>0.354125</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3.018277</v>
+        <v>1.767931</v>
       </c>
     </row>
     <row r="76">
@@ -3208,10 +3208,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012489</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001299</v>
       </c>
     </row>
     <row r="112">
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012489</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001299</v>
       </c>
     </row>
     <row r="135">
@@ -3820,10 +3820,10 @@
         <v>-1.520734</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.994761</v>
+        <v>-3.00725</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.755951</v>
+        <v>-0.75725</v>
       </c>
     </row>
   </sheetData>
@@ -8002,7 +8002,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -9880,7 +9884,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>-0.75</v>
       </c>
@@ -11300,7 +11308,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
